--- a/database.xlsx
+++ b/database.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,42 @@
         <is>
           <t>Reimbursed</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-06-30 18:32:34</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>renzo rocha</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>canadian tire</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -511,20 +547,16 @@
           <t>renzo.r</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>54321</t>
-        </is>
+      <c r="B2" t="n">
+        <v>54321</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>renzo rocha</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D2" t="n">
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -465,10 +465,8 @@
           <t>2026-06-30 18:32:34</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="B2" t="n">
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -492,7 +490,7 @@
         <v>100</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,32 +537,6 @@
         <is>
           <t>Limit</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>renzo.r</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>54321</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>renzo rocha</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Full-Time</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,6 +537,36 @@
         <is>
           <t>Limit</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>patrick.l</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>54321</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Patrick Leslie</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,8 +465,10 @@
           <t>2026-06-30 18:32:34</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -491,6 +493,42 @@
       </c>
       <c r="H2" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-30 18:50:35</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Patrick Leslie</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ctire</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>75</v>
+      </c>
+      <c r="G3" t="n">
+        <v>75</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -545,20 +583,16 @@
           <t>patrick.l</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>54321</t>
-        </is>
+      <c r="B2" t="n">
+        <v>54321</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Patrick Leslie</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D2" t="n">
+        <v>2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -465,10 +465,8 @@
           <t>2026-06-30 18:32:34</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="B2" t="n">
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -501,10 +499,8 @@
           <t>2026-06-30 18:50:35</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="B3" t="n">
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -542,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,6 +596,36 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mitchel.l</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>54321</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>mitchell lois</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>175</v>
       </c>
     </row>

--- a/database.xlsx
+++ b/database.xlsx
@@ -524,7 +524,7 @@
         <v>75</v>
       </c>
       <c r="H3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -605,20 +605,16 @@
           <t>mitchel.l</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>54321</t>
-        </is>
+      <c r="B3" t="n">
+        <v>54321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>mitchell lois</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D3" t="n">
+        <v>3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -576,7 +576,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>patrick.l</t>
+          <t>mitchel.l</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -584,11 +584,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Patrick Leslie</t>
+          <t>mitchell lois</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -596,32 +596,6 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>mitchel.l</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>54321</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>mitchell lois</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Full-Time</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
         <v>175</v>
       </c>
     </row>

--- a/database.xlsx
+++ b/database.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,32 +571,6 @@
         <is>
           <t>Limit</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mitchel.l</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>54321</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>mitchell lois</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Full-Time</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,6 +458,11 @@
           <t>Reimbursed</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ReceiptImage</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -492,6 +497,7 @@
       <c r="H2" t="b">
         <v>1</v>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -526,6 +532,7 @@
       <c r="H3" t="b">
         <v>1</v>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -538,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,6 +578,36 @@
         <is>
           <t>Limit</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>renzo.r</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>54321</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>renzo rocha</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,8 +470,10 @@
           <t>2026-06-30 18:32:34</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -505,8 +507,10 @@
           <t>2026-06-30 18:50:35</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -533,6 +537,47 @@
         <v>1</v>
       </c>
       <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-30 19:32:51</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>renzo rocha</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ctire</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G4" t="n">
+        <v>25</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAMCAgMCAgMDAwMEAwMEBQgFBQQEBQoHBwYIDAoMDAsKCwsNDhIQDQ4RDgsLEBYQERMUFRUVDA8XGBYUGBIUFRT/2wBDAQMEBAUEBQkFBQkUDQsNFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBT/wgARCADIAMgDASIAAhEBAxEB/8QAHAABAQEBAQEBAQEAAAAAAAAAAAgHBgUBAwQC/8QAGgEBAAMBAQEAAAAAAAAAAAAAAAECAwQFBv/aAAwDAQACEAMQAAABqkAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAB5eD7aUY/GbkUujfYdtNnfwyrnSuElale2xv453yrSj+ecEUujXWt9NwMV5tNqSVoHR6u6vn3j+fAA8GVKrlT0+vbsz7T5LU4+uKPqxTEoU3Nd7VRKdox5StETVRM6632Tkei/KsaPy6aYiwMF2fMa/S0FONTTrlxaNoma6Vz+WGXAB4011a6NMcbGEsVOhxsn3E0tE2m0Yvbz5Yrdjn5cp2ATEOyb02v8nKjnNvGXV7J3nZ7/AM/2ed8iAB4Xjdsvblfz64cD6nVJZz13sBl+oIMn1gMY2dL8M11FDmfI71Lm/P7RAKVAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA//EACcQAAEEAgECBQUAAAAAAAAAAAUCAwQGAQcAIDYUFTQ1cBEWFzFA/9oACAEBAAEFAvmMpIVEGVa7FCh555Edk3syU86i9HELqmwMFX5zyo8H8im+I2OaTmtbDaKvzXcsQ67eSpA3IkNxGDezJTzqLycQuq7BWTl8sWwPCvZupnKwOw1Ldxn646D/ALFRe69mTFRwGvK7HMyZFfGyWDo7II2qVmbWKmw3JsT1WEPotQTFfMiCKitMp/c20iKmYOvauwXyTk16BkPJqgORbCnhK5UAKTpNIeClm619sHOoc9U4B0H/AGKi917V9Bqr0PNgd2DuyKZ3Q44lpF3LtGT1dhqhUan9zbViKy3rAwy21a6Qs4ReYwmVZRK803XxRqAV5sYo1Kma/gqiAOg00p4PTAZCNZdlD5M+DrUfJgQeXgKQlWaDFdRUcV4snOK4afzW9cPZfnt5WPqoIkxYSY1ktBM0YmIeykzPxTKI5Dkfvltpi4KknySWKpU3DTyU4Qn+Z6kC3iKU4QnpPYXkJXBUiByyOSPLayuQmDZ4kiZKrGFpC2Zgi/PDqbWM4RTjzfjj5D7h4HbJMTn3cMMVrJGNPs2HFAAScYJ2F59oXWMyGY3z7//EACgRAAEEAQQABAcAAAAAAAAAAAEAAgMRIQQFEjEQICIyExRCUGBxgf/aAAgBAwEBPwH7q1hcLTWF/SdC5uUyMv6RhcE1hcLCawv6ToXDK02ll1b+EQU2yaqJvIUf15IvY5DEWFATdKPAcoCbTPqQxF6UxgcO1t5LNtldB7lsssx1QAOD2tfx+ak4dX4tfxBC5+nimP4G02UtRmcU1/EEJkhYnTEigtHrJNFJzZ/QtTvLPh8dK2ie/JeKV4pcsUrxSBpA0gaQNCleKV4r8E//xAAnEQABBAIABAYDAAAAAAAAAAACAAEDEQQSEyEiMRAgMkFRYTNQYP/aAAgBAgEBPwH9qERGLk3so4Sl9KPFkBrUUBS+lHiyA1oIikZ3b2UcJS+lHiSA1oIykehRYsgtfkxvwmhfTFtlhE7m4qDkMiwyNz+lDVS0htsXoUMQyDWz/ai5Qlp3WMRcRS1xHrxjmeMXH5XGfh8JRSvCWzKPIeO+XdHmGTU3JRzPGLj8qKcoeyPKIm1ZqUcjxPbI8lqqNvJtQ6rbp1TnY6pysWFCWqEtUJ6s7JipnZMdDqtunX+E/8QAQRAAAgEDAQMGCwUFCQAAAAAAAQIDAAQREiExQQUTFFFhcRAiIzJCc4GRobGyIFJ0wdEVM3CS8TRAQ1NygpPC4f/aAAgBAQAGPwL+Md3OnnxQu656wKtbW4kjaKTOQEx6Jp5ZGCRoNTMeApk5NUQQjdI4yx/StXTiewouPlSWd8iw3DbEkXzXPV2GriVfOSNmHur99H/xCsmSJuwx0ltexi2nbYrqfEY/lU8q+ciFh7qtLaaSNopH0sNAFPNM4jiQZZjwpk5NUW8Q3SOMsf0rV05j2FF/So7K9hHOybEliHzHge35OVZGXY0zbvZWrpp7tC4+VLDykqgHZz6bMd4+1yj+Gk+k1Yd7fSaWJTjn5Qrd2/8ASrie7TnYoMARncSeujC9jBo7IwMVcWyMfIvlG443ijcHfLZ6z7UqxjlRZI2farDIOyijcnW4B+5GFPvFSWyMTFgPGTvxQuHOZDburHrIyPyrk71tWtmpwJmLv3D+vwqa8u052GJtCRncW7a6Jei0j2Z5sx8PdUs1rdoJH4tk6R1Cpp4H2ygKjr28fdWmX+zxDW+OPZXMizg5v7vNio2g2W84JVfuniKQOctAxiz2cPn9nlH8NJ9Jqw72+k1Y+sPyq/8AWL8vBe/7PoFRfgf+lcn+s/KizsEUbyxqSSA64Y1ESt14/rSo4wzQO/vya5O9bVhdAeKpaNvbu+Rqfk6RgkjPzkefS2YI+FNe9MS3QRgEOu7FNDC/PjVpVlHnULdfGe2jQ/yjbUkMrBFuF0hj97h4Le0iYMYMlyOs8PhQdxgzuZB3bvy+zfRopZ2gdVUcTpqylmsbiKNS2XeMgDxTVmLa3kuCshyI11Y2VedJgkty0gwJF052eC6lhsp5omCYeOMkeaKitzGwm6Ho0HfnRurI5OuwfUtWnoF2f9SGkn5Uwka7ejg5Ld9XCIMkxMAB3VYyS2NxHGsmSzxkAVLa3C5jkHu7aJjia7g9GWEZPtFdHIvpx/lnWfhSX/KKhXTbHBvwes+B7yxXVbb2jG+P/wArmRfTiPdjWaW4uAUsgd5/xOwUFUaVGwAf3fpZiI4mEeYTQVQFUbAB9rlAR6jJzD6dO/OmpJZXCrKiYhRmIB4nxuNGC1R3nuG5oaPRHE54bM01tdRukts/N+Pt1L6Jzx2fKuTY4E1+NJqDlgnm7M4qFZec50agwlG1Tnd3VaryexjbmJstw9H41bmKN4U0/u5M6l78+C7N5FeSHyfQ+javbjGwHPX4P2gIJ+hLL0bHDRuLad/nbc9Xg5MjlEz2zzSy6jnyexxpPZuIqSQgsEUthRkmmF7DKq3qmbLHUFfO7s2Efy1fCEMZeaOnRvq5Nqs6cn80myYOPKZOcauzFSLaoz3M3ko9PAnj7Kms7mORGt38QyHVlDtG3j1fx+//xAAoEAEAAQMDBAICAgMAAAAAAAABEQAhMUFRYXGBobEQkSDBcPBA0eH/2gAIAQEAAT8h/mOP+0SSSnqnmMSVZMnJT40o2DLTVMgXnw28q7ydF2pocjXcB/6cVErfPEiT4tFg9nD9RSxP7IF7r7qHC5mJE1H6MGRDqU0geLBSpagXnw28qjTmofVC9mmUL4Op9fAMkZMux161YhdngUZ8cCgvVyfVASMjcT8209f1itSK8lBibmjX3BGOal55EM9CXO1Wjo3ID9YSsj260n7qA+k64ZGjYxE+ADTIlqQ79ETtUkaSyFXvd3rwnppJcMNYYPuVArAaApXcAluanFUw9ljFlWLki9eSxUeCvmmk91Jp7FUN8E+fQ1DwjGB6oS1wGYI7FylvTKygHwB2/NtPbHpWN7+0vjwKt1d/S5UGa5hAOtGVBPF5U4lUnJXHaN4SvCemn4LBswaF9SWxeAckLUbXRhyXmcVFYnHM4EOaDazxrAeEtCCBZCDZ3l8fBAFaSEX2DyqDAIeIP27/AIh6fCVEAU3By14ZTmk5RNocCh55G0DKH4nXyQoJuG40FJzFAtWbzQAM1P8ARRC6bc80ZbwAM5lg49VvbWcyAqNzpuQ5UqxkxjK0HI0UuMpQcFx8c0IwnbaLaK+lodPQpAIkjpTuXk+eQ39KsJSzi2mp49mwr0btH8CAQBt/jgxGXjfJ+sUeEYCAPyDlJic5IiNaVCqE0MsspJDaogxNap0li51SkKcC5ZdBcBjVUCAyWANlYl8c0+k1OJ3WqjAyyRTewV/hBwPAuJXSoROkIbUyTM31z8TUbgSC9qmbLRp8CTQmG7rBfgw+AVrDldOc3m7TpYFoCYDVq27qE0tuMQGiyJALfxF6dWYADejfuaUt6CLtZukJZdqbf8mGndkXUbH8/f/aAAwDAQACAAMAAAAQ888888888888888888888888888888888888888888888888888886z2x7yz8588888d7qfEWL+o288N9sNPNec7R988OeNMsO9ede8888888888888888888888888888888888888888888888888888888888888888888//EACcRAQACAgECBQQDAAAAAAAAAAEAESExQWFxEFGB4fAgUGCRocHR/9oACAEDAQE/EPuqA6I9UAcoEvCF3VxFwR6AeUyxJt0Hd+MX4nYm/wBIX6Z6fR8XaNd294ppxUOH83EsvEIBNZ/uJt295Vx9Zp2rrdUZ9C063FqJOSprC9brPWAlyPf+b8VFNy+uNULlzRuGUFRyDc0WpQipviOzSf75PHayHxXyoK7Vt68d9LeXxGITy8UmW4pqX7mfi7ldK3LSm4VceX/BP//EACkRAAIBAwEHAwUAAAAAAAAAAAERACExQVFhcaGx0eHwIJHBEFBggfH/2gAIAQIBAT8Q+6pXV0NkBbOId0kDSAyUprCQwwNIstXQ2gtnEMaSBpFAiAR3ejgTyMMQqJPyoWBYT4iCsMPkYQAklIAAtr8wmrsrf04RHOIoxyhk3IfPaGgAWDebJP6gOH2KYKmv7cMAOih8wBZwkANy8EoOHQqBxDsIDdT36jWW8E3PoBkCxmm2vMIFaDv1lELd/P7HSfPPiV9G6SkDfQ9ZT1uMEv26QKabX+Cf/8QAJxABAQACAgIBBAICAwAAAAAAAREAITFBUWFxECCRoYHRcPBAscH/2gAIAQEAAT8Q/wAxtqUDmTjso1mpkfnCkEY5BcaQxUfADiG6FTOtyfCL2cYMCxr6+f0TGQSU+kQVOtotFQeMMRu3B2UMW6P9PGCR7sv5KX4cCPJou0PknQKF1Rgj6j82EU8UMBWtOFwbBGOK8gyFVX+uXEk0Dv4WJ8IvZxgJJaq/qoP4mcNwZHWXdgd0OwVMQi4pN0hTV7spoTeclxYY9cGCh1UhoeL2hPSoEYwhRHhH76DJ1baJH3+6XBqFT77A4HNpRaEVzJZokpxfaHFz9lQIBOladjkGQACAln5WP18HesAiUNON64iP4AH4cch9+l4I5aLuHVxRayqln2voIh7k1zm/yP8AMGdVYw8M8A8F34ihp6fsCBujOHVxs+qcblqo81V1WExL8oQZ0XuxO44xZvBoBDZVVN6CMcC8s9We7s+3ePHMpXgXbtl3tOsoxINot8Eevv0GQO4d+Zn/AG4Z2EPx/d9daaudP3z9xmo0hQ7lVoPnOLKaavJlK9gPeAMb6INZ08f6RDZH00T8/wDSZKX7DYQeafZFnDg04BhouYQ3cm8q78U8wlYuDnZiilnfLM+PxsZMOsKlXRAnuO/obBMULL9g+NeRxB5+IlL8ND0Ptl+VE1DtVAPeBkJ0yakCoDyuPcNNSRRUKS8ZKqW6igRSsv0X5BqfcooBPWAYIlV2FspI945INHp/OXVS0E/lIGBPm2bYIeDQq7HCrxubQgfKGC1AdPRED842q5OGa3oAj63SmImGBQdbRu2PgspYAIOcbUJ8awYSo3ZgoPIVjFiTDLAiiieMcvvkgIH6d99FBATLReCqHUGZv4jwZ32ba+UN2HzqYEQAcAEn/GQREo4jEsDZspT2EXZzQvBDDEADQB19xsx3SYzttJN3FjQdZFIkYAa8uEacpua64CDAbOaafu4DGoOk8jEI9aCIOCQV6c8Zs3+bhTuCKgq7gwI3hDsbwr1xbxKuIIGueEUvkRv0u2uvoyOA1b8rBwf+5uiixK92QAjtm/polN3Fd4Q6CkWGKmEEJkLaSAbXBpLTCjDbzntTamC81cOdB5PjBDMFshYJrQCZ2YU1kRU3wCtwBFd5sQoXNew6ha3S/wCfv//Z</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -586,20 +631,16 @@
           <t>renzo.r</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>54321</t>
-        </is>
+      <c r="B2" t="n">
+        <v>54321</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>renzo rocha</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D2" t="n">
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -470,10 +470,8 @@
           <t>2026-06-30 18:32:34</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="B2" t="n">
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -507,10 +505,8 @@
           <t>2026-06-30 18:50:35</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="B3" t="n">
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -544,10 +540,8 @@
           <t>2026-06-30 19:32:51</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="B4" t="n">
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -571,7 +565,7 @@
         <v>25</v>
       </c>
       <c r="H4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,15 +502,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-30 18:50:35</t>
+          <t>2026-06-30 19:32:51</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Patrick Leslie</t>
+          <t>renzo rocha</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -524,50 +524,15 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="G3" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
       </c>
-      <c r="I3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-06-30 19:32:51</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>renzo rocha</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Full-Time</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>ctire</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>25</v>
-      </c>
-      <c r="G4" t="n">
-        <v>25</v>
-      </c>
-      <c r="H4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAMCAgMCAgMDAwMEAwMEBQgFBQQEBQoHBwYIDAoMDAsKCwsNDhIQDQ4RDgsLEBYQERMUFRUVDA8XGBYUGBIUFRT/2wBDAQMEBAUEBQkFBQkUDQsNFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBT/wgARCADIAMgDASIAAhEBAxEB/8QAHAABAQEBAQEBAQEAAAAAAAAAAAgHBgUBAwQC/8QAGgEBAAMBAQEAAAAAAAAAAAAAAAECAwQFBv/aAAwDAQACEAMQAAABqkAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAB5eD7aUY/GbkUujfYdtNnfwyrnSuElale2xv453yrSj+ecEUujXWt9NwMV5tNqSVoHR6u6vn3j+fAA8GVKrlT0+vbsz7T5LU4+uKPqxTEoU3Nd7VRKdox5StETVRM6632Tkei/KsaPy6aYiwMF2fMa/S0FONTTrlxaNoma6Vz+WGXAB4011a6NMcbGEsVOhxsn3E0tE2m0Yvbz5Yrdjn5cp2ATEOyb02v8nKjnNvGXV7J3nZ7/AM/2ed8iAB4Xjdsvblfz64cD6nVJZz13sBl+oIMn1gMY2dL8M11FDmfI71Lm/P7RAKVAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA//EACcQAAEEAgECBQUAAAAAAAAAAAUCAwQGAQcAIDYUFTQ1cBEWFzFA/9oACAEBAAEFAvmMpIVEGVa7FCh555Edk3syU86i9HELqmwMFX5zyo8H8im+I2OaTmtbDaKvzXcsQ67eSpA3IkNxGDezJTzqLycQuq7BWTl8sWwPCvZupnKwOw1Ldxn646D/ALFRe69mTFRwGvK7HMyZFfGyWDo7II2qVmbWKmw3JsT1WEPotQTFfMiCKitMp/c20iKmYOvauwXyTk16BkPJqgORbCnhK5UAKTpNIeClm619sHOoc9U4B0H/AGKi917V9Bqr0PNgd2DuyKZ3Q44lpF3LtGT1dhqhUan9zbViKy3rAwy21a6Qs4ReYwmVZRK803XxRqAV5sYo1Kma/gqiAOg00p4PTAZCNZdlD5M+DrUfJgQeXgKQlWaDFdRUcV4snOK4afzW9cPZfnt5WPqoIkxYSY1ktBM0YmIeykzPxTKI5Dkfvltpi4KknySWKpU3DTyU4Qn+Z6kC3iKU4QnpPYXkJXBUiByyOSPLayuQmDZ4kiZKrGFpC2Zgi/PDqbWM4RTjzfjj5D7h4HbJMTn3cMMVrJGNPs2HFAAScYJ2F59oXWMyGY3z7//EACgRAAEEAQQABAcAAAAAAAAAAAEAAgMRIQQFEjEQICIyExRCUGBxgf/aAAgBAwEBPwH7q1hcLTWF/SdC5uUyMv6RhcE1hcLCawv6ToXDK02ll1b+EQU2yaqJvIUf15IvY5DEWFATdKPAcoCbTPqQxF6UxgcO1t5LNtldB7lsssx1QAOD2tfx+ak4dX4tfxBC5+nimP4G02UtRmcU1/EEJkhYnTEigtHrJNFJzZ/QtTvLPh8dK2ie/JeKV4pcsUrxSBpA0gaQNCleKV4r8E//xAAnEQABBAIABAYDAAAAAAAAAAACAAEDEQQSEyEiMRAgMkFRYTNQYP/aAAgBAgEBPwH9qERGLk3so4Sl9KPFkBrUUBS+lHiyA1oIikZ3b2UcJS+lHiSA1oIykehRYsgtfkxvwmhfTFtlhE7m4qDkMiwyNz+lDVS0htsXoUMQyDWz/ai5Qlp3WMRcRS1xHrxjmeMXH5XGfh8JRSvCWzKPIeO+XdHmGTU3JRzPGLj8qKcoeyPKIm1ZqUcjxPbI8lqqNvJtQ6rbp1TnY6pysWFCWqEtUJ6s7JipnZMdDqtunX+E/8QAQRAAAgEDAQMGCwUFCQAAAAAAAQIDAAQREiExQQUTFFFhcRAiIzJCc4GRobGyIFJ0wdEVM3CS8TRAQ1NygpPC4f/aAAgBAQAGPwL+Md3OnnxQu656wKtbW4kjaKTOQEx6Jp5ZGCRoNTMeApk5NUQQjdI4yx/StXTiewouPlSWd8iw3DbEkXzXPV2GriVfOSNmHur99H/xCsmSJuwx0ltexi2nbYrqfEY/lU8q+ciFh7qtLaaSNopH0sNAFPNM4jiQZZjwpk5NUW8Q3SOMsf0rV05j2FF/So7K9hHOybEliHzHge35OVZGXY0zbvZWrpp7tC4+VLDykqgHZz6bMd4+1yj+Gk+k1Yd7fSaWJTjn5Qrd2/8ASrie7TnYoMARncSeujC9jBo7IwMVcWyMfIvlG443ijcHfLZ6z7UqxjlRZI2farDIOyijcnW4B+5GFPvFSWyMTFgPGTvxQuHOZDburHrIyPyrk71tWtmpwJmLv3D+vwqa8u052GJtCRncW7a6Jei0j2Z5sx8PdUs1rdoJH4tk6R1Cpp4H2ygKjr28fdWmX+zxDW+OPZXMizg5v7vNio2g2W84JVfuniKQOctAxiz2cPn9nlH8NJ9Jqw72+k1Y+sPyq/8AWL8vBe/7PoFRfgf+lcn+s/KizsEUbyxqSSA64Y1ESt14/rSo4wzQO/vya5O9bVhdAeKpaNvbu+Rqfk6RgkjPzkefS2YI+FNe9MS3QRgEOu7FNDC/PjVpVlHnULdfGe2jQ/yjbUkMrBFuF0hj97h4Le0iYMYMlyOs8PhQdxgzuZB3bvy+zfRopZ2gdVUcTpqylmsbiKNS2XeMgDxTVmLa3kuCshyI11Y2VedJgkty0gwJF052eC6lhsp5omCYeOMkeaKitzGwm6Ho0HfnRurI5OuwfUtWnoF2f9SGkn5Uwka7ejg5Ld9XCIMkxMAB3VYyS2NxHGsmSzxkAVLa3C5jkHu7aJjia7g9GWEZPtFdHIvpx/lnWfhSX/KKhXTbHBvwes+B7yxXVbb2jG+P/wArmRfTiPdjWaW4uAUsgd5/xOwUFUaVGwAf3fpZiI4mEeYTQVQFUbAB9rlAR6jJzD6dO/OmpJZXCrKiYhRmIB4nxuNGC1R3nuG5oaPRHE54bM01tdRukts/N+Pt1L6Jzx2fKuTY4E1+NJqDlgnm7M4qFZec50agwlG1Tnd3VaryexjbmJstw9H41bmKN4U0/u5M6l78+C7N5FeSHyfQ+javbjGwHPX4P2gIJ+hLL0bHDRuLad/nbc9Xg5MjlEz2zzSy6jnyexxpPZuIqSQgsEUthRkmmF7DKq3qmbLHUFfO7s2Efy1fCEMZeaOnRvq5Nqs6cn80myYOPKZOcauzFSLaoz3M3ko9PAnj7Kms7mORGt38QyHVlDtG3j1fx+//xAAoEAEAAQMDBAICAgMAAAAAAAABEQAhMUFRYXGBobEQkSDBcPBA0eH/2gAIAQEAAT8h/mOP+0SSSnqnmMSVZMnJT40o2DLTVMgXnw28q7ydF2pocjXcB/6cVErfPEiT4tFg9nD9RSxP7IF7r7qHC5mJE1H6MGRDqU0geLBSpagXnw28qjTmofVC9mmUL4Op9fAMkZMux161YhdngUZ8cCgvVyfVASMjcT8209f1itSK8lBibmjX3BGOal55EM9CXO1Wjo3ID9YSsj260n7qA+k64ZGjYxE+ADTIlqQ79ETtUkaSyFXvd3rwnppJcMNYYPuVArAaApXcAluanFUw9ljFlWLki9eSxUeCvmmk91Jp7FUN8E+fQ1DwjGB6oS1wGYI7FylvTKygHwB2/NtPbHpWN7+0vjwKt1d/S5UGa5hAOtGVBPF5U4lUnJXHaN4SvCemn4LBswaF9SWxeAckLUbXRhyXmcVFYnHM4EOaDazxrAeEtCCBZCDZ3l8fBAFaSEX2DyqDAIeIP27/AIh6fCVEAU3By14ZTmk5RNocCh55G0DKH4nXyQoJuG40FJzFAtWbzQAM1P8ARRC6bc80ZbwAM5lg49VvbWcyAqNzpuQ5UqxkxjK0HI0UuMpQcFx8c0IwnbaLaK+lodPQpAIkjpTuXk+eQ39KsJSzi2mp49mwr0btH8CAQBt/jgxGXjfJ+sUeEYCAPyDlJic5IiNaVCqE0MsspJDaogxNap0li51SkKcC5ZdBcBjVUCAyWANlYl8c0+k1OJ3WqjAyyRTewV/hBwPAuJXSoROkIbUyTM31z8TUbgSC9qmbLRp8CTQmG7rBfgw+AVrDldOc3m7TpYFoCYDVq27qE0tuMQGiyJALfxF6dWYADejfuaUt6CLtZukJZdqbf8mGndkXUbH8/f/aAAwDAQACAAMAAAAQ888888888888888888888888888888888888888888888888888886z2x7yz8588888d7qfEWL+o288N9sNPNec7R988OeNMsO9ede8888888888888888888888888888888888888888888888888888888888888888888//EACcRAQACAgECBQQDAAAAAAAAAAEAESExQWFxEFGB4fAgUGCRocHR/9oACAEDAQE/EPuqA6I9UAcoEvCF3VxFwR6AeUyxJt0Hd+MX4nYm/wBIX6Z6fR8XaNd294ppxUOH83EsvEIBNZ/uJt295Vx9Zp2rrdUZ9C063FqJOSprC9brPWAlyPf+b8VFNy+uNULlzRuGUFRyDc0WpQipviOzSf75PHayHxXyoK7Vt68d9LeXxGITy8UmW4pqX7mfi7ldK3LSm4VceX/BP//EACkRAAIBAwEHAwUAAAAAAAAAAAERACExQVFhcaGx0eHwIJHBEFBggfH/2gAIAQIBAT8Q+6pXV0NkBbOId0kDSAyUprCQwwNIstXQ2gtnEMaSBpFAiAR3ejgTyMMQqJPyoWBYT4iCsMPkYQAklIAAtr8wmrsrf04RHOIoxyhk3IfPaGgAWDebJP6gOH2KYKmv7cMAOih8wBZwkANy8EoOHQqBxDsIDdT36jWW8E3PoBkCxmm2vMIFaDv1lELd/P7HSfPPiV9G6SkDfQ9ZT1uMEv26QKabX+Cf/8QAJxABAQACAgIBBAICAwAAAAAAAREAITFBUWFxECCRoYHRcPBAscH/2gAIAQEAAT8Q/wAxtqUDmTjso1mpkfnCkEY5BcaQxUfADiG6FTOtyfCL2cYMCxr6+f0TGQSU+kQVOtotFQeMMRu3B2UMW6P9PGCR7sv5KX4cCPJou0PknQKF1Rgj6j82EU8UMBWtOFwbBGOK8gyFVX+uXEk0Dv4WJ8IvZxgJJaq/qoP4mcNwZHWXdgd0OwVMQi4pN0hTV7spoTeclxYY9cGCh1UhoeL2hPSoEYwhRHhH76DJ1baJH3+6XBqFT77A4HNpRaEVzJZokpxfaHFz9lQIBOladjkGQACAln5WP18HesAiUNON64iP4AH4cch9+l4I5aLuHVxRayqln2voIh7k1zm/yP8AMGdVYw8M8A8F34ihp6fsCBujOHVxs+qcblqo81V1WExL8oQZ0XuxO44xZvBoBDZVVN6CMcC8s9We7s+3ePHMpXgXbtl3tOsoxINot8Eevv0GQO4d+Zn/AG4Z2EPx/d9daaudP3z9xmo0hQ7lVoPnOLKaavJlK9gPeAMb6INZ08f6RDZH00T8/wDSZKX7DYQeafZFnDg04BhouYQ3cm8q78U8wlYuDnZiilnfLM+PxsZMOsKlXRAnuO/obBMULL9g+NeRxB5+IlL8ND0Ptl+VE1DtVAPeBkJ0yakCoDyuPcNNSRRUKS8ZKqW6igRSsv0X5BqfcooBPWAYIlV2FspI945INHp/OXVS0E/lIGBPm2bYIeDQq7HCrxubQgfKGC1AdPRED842q5OGa3oAj63SmImGBQdbRu2PgspYAIOcbUJ8awYSo3ZgoPIVjFiTDLAiiieMcvvkgIH6d99FBATLReCqHUGZv4jwZ32ba+UN2HzqYEQAcAEn/GQREo4jEsDZspT2EXZzQvBDDEADQB19xsx3SYzttJN3FjQdZFIkYAa8uEacpua64CDAbOaafu4DGoOk8jEI9aCIOCQV6c8Zs3+bhTuCKgq7gwI3hDsbwr1xbxKuIIGueEUvkRv0u2uvoyOA1b8rBwf+5uiixK92QAjtm/polN3Fd4Q6CkWGKmEEJkLaSAbXBpLTCjDbzntTamC81cOdB5PjBDMFshYJrQCZ2YU1kRU3wCtwBFd5sQoXNew6ha3S/wCfv//Z</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-30 18:32:34</t>
+          <t>2026-06-30 19:32:51</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -485,54 +485,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>canadian tire</t>
+          <t>ctire</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
       </c>
-      <c r="I2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-06-30 19:32:51</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>renzo rocha</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Full-Time</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>ctire</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G3" t="n">
-        <v>25</v>
-      </c>
-      <c r="H3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAMCAgMCAgMDAwMEAwMEBQgFBQQEBQoHBwYIDAoMDAsKCwsNDhIQDQ4RDgsLEBYQERMUFRUVDA8XGBYUGBIUFRT/2wBDAQMEBAUEBQkFBQkUDQsNFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBT/wgARCADIAMgDASIAAhEBAxEB/8QAHAABAQEBAQEBAQEAAAAAAAAAAAgHBgUBAwQC/8QAGgEBAAMBAQEAAAAAAAAAAAAAAAECAwQFBv/aAAwDAQACEAMQAAABqkAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAB5eD7aUY/GbkUujfYdtNnfwyrnSuElale2xv453yrSj+ecEUujXWt9NwMV5tNqSVoHR6u6vn3j+fAA8GVKrlT0+vbsz7T5LU4+uKPqxTEoU3Nd7VRKdox5StETVRM6632Tkei/KsaPy6aYiwMF2fMa/S0FONTTrlxaNoma6Vz+WGXAB4011a6NMcbGEsVOhxsn3E0tE2m0Yvbz5Yrdjn5cp2ATEOyb02v8nKjnNvGXV7J3nZ7/AM/2ed8iAB4Xjdsvblfz64cD6nVJZz13sBl+oIMn1gMY2dL8M11FDmfI71Lm/P7RAKVAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA//EACcQAAEEAgECBQUAAAAAAAAAAAUCAwQGAQcAIDYUFTQ1cBEWFzFA/9oACAEBAAEFAvmMpIVEGVa7FCh555Edk3syU86i9HELqmwMFX5zyo8H8im+I2OaTmtbDaKvzXcsQ67eSpA3IkNxGDezJTzqLycQuq7BWTl8sWwPCvZupnKwOw1Ldxn646D/ALFRe69mTFRwGvK7HMyZFfGyWDo7II2qVmbWKmw3JsT1WEPotQTFfMiCKitMp/c20iKmYOvauwXyTk16BkPJqgORbCnhK5UAKTpNIeClm619sHOoc9U4B0H/AGKi917V9Bqr0PNgd2DuyKZ3Q44lpF3LtGT1dhqhUan9zbViKy3rAwy21a6Qs4ReYwmVZRK803XxRqAV5sYo1Kma/gqiAOg00p4PTAZCNZdlD5M+DrUfJgQeXgKQlWaDFdRUcV4snOK4afzW9cPZfnt5WPqoIkxYSY1ktBM0YmIeykzPxTKI5Dkfvltpi4KknySWKpU3DTyU4Qn+Z6kC3iKU4QnpPYXkJXBUiByyOSPLayuQmDZ4kiZKrGFpC2Zgi/PDqbWM4RTjzfjj5D7h4HbJMTn3cMMVrJGNPs2HFAAScYJ2F59oXWMyGY3z7//EACgRAAEEAQQABAcAAAAAAAAAAAEAAgMRIQQFEjEQICIyExRCUGBxgf/aAAgBAwEBPwH7q1hcLTWF/SdC5uUyMv6RhcE1hcLCawv6ToXDK02ll1b+EQU2yaqJvIUf15IvY5DEWFATdKPAcoCbTPqQxF6UxgcO1t5LNtldB7lsssx1QAOD2tfx+ak4dX4tfxBC5+nimP4G02UtRmcU1/EEJkhYnTEigtHrJNFJzZ/QtTvLPh8dK2ie/JeKV4pcsUrxSBpA0gaQNCleKV4r8E//xAAnEQABBAIABAYDAAAAAAAAAAACAAEDEQQSEyEiMRAgMkFRYTNQYP/aAAgBAgEBPwH9qERGLk3so4Sl9KPFkBrUUBS+lHiyA1oIikZ3b2UcJS+lHiSA1oIykehRYsgtfkxvwmhfTFtlhE7m4qDkMiwyNz+lDVS0htsXoUMQyDWz/ai5Qlp3WMRcRS1xHrxjmeMXH5XGfh8JRSvCWzKPIeO+XdHmGTU3JRzPGLj8qKcoeyPKIm1ZqUcjxPbI8lqqNvJtQ6rbp1TnY6pysWFCWqEtUJ6s7JipnZMdDqtunX+E/8QAQRAAAgEDAQMGCwUFCQAAAAAAAQIDAAQREiExQQUTFFFhcRAiIzJCc4GRobGyIFJ0wdEVM3CS8TRAQ1NygpPC4f/aAAgBAQAGPwL+Md3OnnxQu656wKtbW4kjaKTOQEx6Jp5ZGCRoNTMeApk5NUQQjdI4yx/StXTiewouPlSWd8iw3DbEkXzXPV2GriVfOSNmHur99H/xCsmSJuwx0ltexi2nbYrqfEY/lU8q+ciFh7qtLaaSNopH0sNAFPNM4jiQZZjwpk5NUW8Q3SOMsf0rV05j2FF/So7K9hHOybEliHzHge35OVZGXY0zbvZWrpp7tC4+VLDykqgHZz6bMd4+1yj+Gk+k1Yd7fSaWJTjn5Qrd2/8ASrie7TnYoMARncSeujC9jBo7IwMVcWyMfIvlG443ijcHfLZ6z7UqxjlRZI2farDIOyijcnW4B+5GFPvFSWyMTFgPGTvxQuHOZDburHrIyPyrk71tWtmpwJmLv3D+vwqa8u052GJtCRncW7a6Jei0j2Z5sx8PdUs1rdoJH4tk6R1Cpp4H2ygKjr28fdWmX+zxDW+OPZXMizg5v7vNio2g2W84JVfuniKQOctAxiz2cPn9nlH8NJ9Jqw72+k1Y+sPyq/8AWL8vBe/7PoFRfgf+lcn+s/KizsEUbyxqSSA64Y1ESt14/rSo4wzQO/vya5O9bVhdAeKpaNvbu+Rqfk6RgkjPzkefS2YI+FNe9MS3QRgEOu7FNDC/PjVpVlHnULdfGe2jQ/yjbUkMrBFuF0hj97h4Le0iYMYMlyOs8PhQdxgzuZB3bvy+zfRopZ2gdVUcTpqylmsbiKNS2XeMgDxTVmLa3kuCshyI11Y2VedJgkty0gwJF052eC6lhsp5omCYeOMkeaKitzGwm6Ho0HfnRurI5OuwfUtWnoF2f9SGkn5Uwka7ejg5Ld9XCIMkxMAB3VYyS2NxHGsmSzxkAVLa3C5jkHu7aJjia7g9GWEZPtFdHIvpx/lnWfhSX/KKhXTbHBvwes+B7yxXVbb2jG+P/wArmRfTiPdjWaW4uAUsgd5/xOwUFUaVGwAf3fpZiI4mEeYTQVQFUbAB9rlAR6jJzD6dO/OmpJZXCrKiYhRmIB4nxuNGC1R3nuG5oaPRHE54bM01tdRukts/N+Pt1L6Jzx2fKuTY4E1+NJqDlgnm7M4qFZec50agwlG1Tnd3VaryexjbmJstw9H41bmKN4U0/u5M6l78+C7N5FeSHyfQ+javbjGwHPX4P2gIJ+hLL0bHDRuLad/nbc9Xg5MjlEz2zzSy6jnyexxpPZuIqSQgsEUthRkmmF7DKq3qmbLHUFfO7s2Efy1fCEMZeaOnRvq5Nqs6cn80myYOPKZOcauzFSLaoz3M3ko9PAnj7Kms7mORGt38QyHVlDtG3j1fx+//xAAoEAEAAQMDBAICAgMAAAAAAAABEQAhMUFRYXGBobEQkSDBcPBA0eH/2gAIAQEAAT8h/mOP+0SSSnqnmMSVZMnJT40o2DLTVMgXnw28q7ydF2pocjXcB/6cVErfPEiT4tFg9nD9RSxP7IF7r7qHC5mJE1H6MGRDqU0geLBSpagXnw28qjTmofVC9mmUL4Op9fAMkZMux161YhdngUZ8cCgvVyfVASMjcT8209f1itSK8lBibmjX3BGOal55EM9CXO1Wjo3ID9YSsj260n7qA+k64ZGjYxE+ADTIlqQ79ETtUkaSyFXvd3rwnppJcMNYYPuVArAaApXcAluanFUw9ljFlWLki9eSxUeCvmmk91Jp7FUN8E+fQ1DwjGB6oS1wGYI7FylvTKygHwB2/NtPbHpWN7+0vjwKt1d/S5UGa5hAOtGVBPF5U4lUnJXHaN4SvCemn4LBswaF9SWxeAckLUbXRhyXmcVFYnHM4EOaDazxrAeEtCCBZCDZ3l8fBAFaSEX2DyqDAIeIP27/AIh6fCVEAU3By14ZTmk5RNocCh55G0DKH4nXyQoJuG40FJzFAtWbzQAM1P8ARRC6bc80ZbwAM5lg49VvbWcyAqNzpuQ5UqxkxjK0HI0UuMpQcFx8c0IwnbaLaK+lodPQpAIkjpTuXk+eQ39KsJSzi2mp49mwr0btH8CAQBt/jgxGXjfJ+sUeEYCAPyDlJic5IiNaVCqE0MsspJDaogxNap0li51SkKcC5ZdBcBjVUCAyWANlYl8c0+k1OJ3WqjAyyRTewV/hBwPAuJXSoROkIbUyTM31z8TUbgSC9qmbLRp8CTQmG7rBfgw+AVrDldOc3m7TpYFoCYDVq27qE0tuMQGiyJALfxF6dWYADejfuaUt6CLtZukJZdqbf8mGndkXUbH8/f/aAAwDAQACAAMAAAAQ888888888888888888888888888888888888888888888888888886z2x7yz8588888d7qfEWL+o288N9sNPNec7R988OeNMsO9ede8888888888888888888888888888888888888888888888888888888888888888888//EACcRAQACAgECBQQDAAAAAAAAAAEAESExQWFxEFGB4fAgUGCRocHR/9oACAEDAQE/EPuqA6I9UAcoEvCF3VxFwR6AeUyxJt0Hd+MX4nYm/wBIX6Z6fR8XaNd294ppxUOH83EsvEIBNZ/uJt295Vx9Zp2rrdUZ9C063FqJOSprC9brPWAlyPf+b8VFNy+uNULlzRuGUFRyDc0WpQipviOzSf75PHayHxXyoK7Vt68d9LeXxGITy8UmW4pqX7mfi7ldK3LSm4VceX/BP//EACkRAAIBAwEHAwUAAAAAAAAAAAERACExQVFhcaGx0eHwIJHBEFBggfH/2gAIAQIBAT8Q+6pXV0NkBbOId0kDSAyUprCQwwNIstXQ2gtnEMaSBpFAiAR3ejgTyMMQqJPyoWBYT4iCsMPkYQAklIAAtr8wmrsrf04RHOIoxyhk3IfPaGgAWDebJP6gOH2KYKmv7cMAOih8wBZwkANy8EoOHQqBxDsIDdT36jWW8E3PoBkCxmm2vMIFaDv1lELd/P7HSfPPiV9G6SkDfQ9ZT1uMEv26QKabX+Cf/8QAJxABAQACAgIBBAICAwAAAAAAAREAITFBUWFxECCRoYHRcPBAscH/2gAIAQEAAT8Q/wAxtqUDmTjso1mpkfnCkEY5BcaQxUfADiG6FTOtyfCL2cYMCxr6+f0TGQSU+kQVOtotFQeMMRu3B2UMW6P9PGCR7sv5KX4cCPJou0PknQKF1Rgj6j82EU8UMBWtOFwbBGOK8gyFVX+uXEk0Dv4WJ8IvZxgJJaq/qoP4mcNwZHWXdgd0OwVMQi4pN0hTV7spoTeclxYY9cGCh1UhoeL2hPSoEYwhRHhH76DJ1baJH3+6XBqFT77A4HNpRaEVzJZokpxfaHFz9lQIBOladjkGQACAln5WP18HesAiUNON64iP4AH4cch9+l4I5aLuHVxRayqln2voIh7k1zm/yP8AMGdVYw8M8A8F34ihp6fsCBujOHVxs+qcblqo81V1WExL8oQZ0XuxO44xZvBoBDZVVN6CMcC8s9We7s+3ePHMpXgXbtl3tOsoxINot8Eevv0GQO4d+Zn/AG4Z2EPx/d9daaudP3z9xmo0hQ7lVoPnOLKaavJlK9gPeAMb6INZ08f6RDZH00T8/wDSZKX7DYQeafZFnDg04BhouYQ3cm8q78U8wlYuDnZiilnfLM+PxsZMOsKlXRAnuO/obBMULL9g+NeRxB5+IlL8ND0Ptl+VE1DtVAPeBkJ0yakCoDyuPcNNSRRUKS8ZKqW6igRSsv0X5BqfcooBPWAYIlV2FspI945INHp/OXVS0E/lIGBPm2bYIeDQq7HCrxubQgfKGC1AdPRED842q5OGa3oAj63SmImGBQdbRu2PgspYAIOcbUJ8awYSo3ZgoPIVjFiTDLAiiieMcvvkgIH6d99FBATLReCqHUGZv4jwZ32ba+UN2HzqYEQAcAEn/GQREo4jEsDZspT2EXZzQvBDDEADQB19xsx3SYzttJN3FjQdZFIkYAa8uEacpua64CDAbOaafu4DGoOk8jEI9aCIOCQV6c8Zs3+bhTuCKgq7gwI3hDsbwr1xbxKuIIGueEUvkRv0u2uvoyOA1b8rBwf+5uiixK92QAjtm/polN3Fd4Q6CkWGKmEEJkLaSAbXBpLTCjDbzntTamC81cOdB5PjBDMFshYJrQCZ2YU1kRU3wCtwBFd5sQoXNew6ha3S/wCfv//Z</t>
         </is>

--- a/database.xlsx
+++ b/database.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,45 +461,6 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>ReceiptImage</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-06-30 19:32:51</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>renzo rocha</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Full-Time</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>ctire</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>25</v>
-      </c>
-      <c r="G2" t="n">
-        <v>25</v>
-      </c>
-      <c r="H2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAMCAgMCAgMDAwMEAwMEBQgFBQQEBQoHBwYIDAoMDAsKCwsNDhIQDQ4RDgsLEBYQERMUFRUVDA8XGBYUGBIUFRT/2wBDAQMEBAUEBQkFBQkUDQsNFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBQUFBT/wgARCADIAMgDASIAAhEBAxEB/8QAHAABAQEBAQEBAQEAAAAAAAAAAAgHBgUBAwQC/8QAGgEBAAMBAQEAAAAAAAAAAAAAAAECAwQFBv/aAAwDAQACEAMQAAABqkAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAB5eD7aUY/GbkUujfYdtNnfwyrnSuElale2xv453yrSj+ecEUujXWt9NwMV5tNqSVoHR6u6vn3j+fAA8GVKrlT0+vbsz7T5LU4+uKPqxTEoU3Nd7VRKdox5StETVRM6632Tkei/KsaPy6aYiwMF2fMa/S0FONTTrlxaNoma6Vz+WGXAB4011a6NMcbGEsVOhxsn3E0tE2m0Yvbz5Yrdjn5cp2ATEOyb02v8nKjnNvGXV7J3nZ7/AM/2ed8iAB4Xjdsvblfz64cD6nVJZz13sBl+oIMn1gMY2dL8M11FDmfI71Lm/P7RAKVAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA//EACcQAAEEAgECBQUAAAAAAAAAAAUCAwQGAQcAIDYUFTQ1cBEWFzFA/9oACAEBAAEFAvmMpIVEGVa7FCh555Edk3syU86i9HELqmwMFX5zyo8H8im+I2OaTmtbDaKvzXcsQ67eSpA3IkNxGDezJTzqLycQuq7BWTl8sWwPCvZupnKwOw1Ldxn646D/ALFRe69mTFRwGvK7HMyZFfGyWDo7II2qVmbWKmw3JsT1WEPotQTFfMiCKitMp/c20iKmYOvauwXyTk16BkPJqgORbCnhK5UAKTpNIeClm619sHOoc9U4B0H/AGKi917V9Bqr0PNgd2DuyKZ3Q44lpF3LtGT1dhqhUan9zbViKy3rAwy21a6Qs4ReYwmVZRK803XxRqAV5sYo1Kma/gqiAOg00p4PTAZCNZdlD5M+DrUfJgQeXgKQlWaDFdRUcV4snOK4afzW9cPZfnt5WPqoIkxYSY1ktBM0YmIeykzPxTKI5Dkfvltpi4KknySWKpU3DTyU4Qn+Z6kC3iKU4QnpPYXkJXBUiByyOSPLayuQmDZ4kiZKrGFpC2Zgi/PDqbWM4RTjzfjj5D7h4HbJMTn3cMMVrJGNPs2HFAAScYJ2F59oXWMyGY3z7//EACgRAAEEAQQABAcAAAAAAAAAAAEAAgMRIQQFEjEQICIyExRCUGBxgf/aAAgBAwEBPwH7q1hcLTWF/SdC5uUyMv6RhcE1hcLCawv6ToXDK02ll1b+EQU2yaqJvIUf15IvY5DEWFATdKPAcoCbTPqQxF6UxgcO1t5LNtldB7lsssx1QAOD2tfx+ak4dX4tfxBC5+nimP4G02UtRmcU1/EEJkhYnTEigtHrJNFJzZ/QtTvLPh8dK2ie/JeKV4pcsUrxSBpA0gaQNCleKV4r8E//xAAnEQABBAIABAYDAAAAAAAAAAACAAEDEQQSEyEiMRAgMkFRYTNQYP/aAAgBAgEBPwH9qERGLk3so4Sl9KPFkBrUUBS+lHiyA1oIikZ3b2UcJS+lHiSA1oIykehRYsgtfkxvwmhfTFtlhE7m4qDkMiwyNz+lDVS0htsXoUMQyDWz/ai5Qlp3WMRcRS1xHrxjmeMXH5XGfh8JRSvCWzKPIeO+XdHmGTU3JRzPGLj8qKcoeyPKIm1ZqUcjxPbI8lqqNvJtQ6rbp1TnY6pysWFCWqEtUJ6s7JipnZMdDqtunX+E/8QAQRAAAgEDAQMGCwUFCQAAAAAAAQIDAAQREiExQQUTFFFhcRAiIzJCc4GRobGyIFJ0wdEVM3CS8TRAQ1NygpPC4f/aAAgBAQAGPwL+Md3OnnxQu656wKtbW4kjaKTOQEx6Jp5ZGCRoNTMeApk5NUQQjdI4yx/StXTiewouPlSWd8iw3DbEkXzXPV2GriVfOSNmHur99H/xCsmSJuwx0ltexi2nbYrqfEY/lU8q+ciFh7qtLaaSNopH0sNAFPNM4jiQZZjwpk5NUW8Q3SOMsf0rV05j2FF/So7K9hHOybEliHzHge35OVZGXY0zbvZWrpp7tC4+VLDykqgHZz6bMd4+1yj+Gk+k1Yd7fSaWJTjn5Qrd2/8ASrie7TnYoMARncSeujC9jBo7IwMVcWyMfIvlG443ijcHfLZ6z7UqxjlRZI2farDIOyijcnW4B+5GFPvFSWyMTFgPGTvxQuHOZDburHrIyPyrk71tWtmpwJmLv3D+vwqa8u052GJtCRncW7a6Jei0j2Z5sx8PdUs1rdoJH4tk6R1Cpp4H2ygKjr28fdWmX+zxDW+OPZXMizg5v7vNio2g2W84JVfuniKQOctAxiz2cPn9nlH8NJ9Jqw72+k1Y+sPyq/8AWL8vBe/7PoFRfgf+lcn+s/KizsEUbyxqSSA64Y1ESt14/rSo4wzQO/vya5O9bVhdAeKpaNvbu+Rqfk6RgkjPzkefS2YI+FNe9MS3QRgEOu7FNDC/PjVpVlHnULdfGe2jQ/yjbUkMrBFuF0hj97h4Le0iYMYMlyOs8PhQdxgzuZB3bvy+zfRopZ2gdVUcTpqylmsbiKNS2XeMgDxTVmLa3kuCshyI11Y2VedJgkty0gwJF052eC6lhsp5omCYeOMkeaKitzGwm6Ho0HfnRurI5OuwfUtWnoF2f9SGkn5Uwka7ejg5Ld9XCIMkxMAB3VYyS2NxHGsmSzxkAVLa3C5jkHu7aJjia7g9GWEZPtFdHIvpx/lnWfhSX/KKhXTbHBvwes+B7yxXVbb2jG+P/wArmRfTiPdjWaW4uAUsgd5/xOwUFUaVGwAf3fpZiI4mEeYTQVQFUbAB9rlAR6jJzD6dO/OmpJZXCrKiYhRmIB4nxuNGC1R3nuG5oaPRHE54bM01tdRukts/N+Pt1L6Jzx2fKuTY4E1+NJqDlgnm7M4qFZec50agwlG1Tnd3VaryexjbmJstw9H41bmKN4U0/u5M6l78+C7N5FeSHyfQ+javbjGwHPX4P2gIJ+hLL0bHDRuLad/nbc9Xg5MjlEz2zzSy6jnyexxpPZuIqSQgsEUthRkmmF7DKq3qmbLHUFfO7s2Efy1fCEMZeaOnRvq5Nqs6cn80myYOPKZOcauzFSLaoz3M3ko9PAnj7Kms7mORGt38QyHVlDtG3j1fx+//xAAoEAEAAQMDBAICAgMAAAAAAAABEQAhMUFRYXGBobEQkSDBcPBA0eH/2gAIAQEAAT8h/mOP+0SSSnqnmMSVZMnJT40o2DLTVMgXnw28q7ydF2pocjXcB/6cVErfPEiT4tFg9nD9RSxP7IF7r7qHC5mJE1H6MGRDqU0geLBSpagXnw28qjTmofVC9mmUL4Op9fAMkZMux161YhdngUZ8cCgvVyfVASMjcT8209f1itSK8lBibmjX3BGOal55EM9CXO1Wjo3ID9YSsj260n7qA+k64ZGjYxE+ADTIlqQ79ETtUkaSyFXvd3rwnppJcMNYYPuVArAaApXcAluanFUw9ljFlWLki9eSxUeCvmmk91Jp7FUN8E+fQ1DwjGB6oS1wGYI7FylvTKygHwB2/NtPbHpWN7+0vjwKt1d/S5UGa5hAOtGVBPF5U4lUnJXHaN4SvCemn4LBswaF9SWxeAckLUbXRhyXmcVFYnHM4EOaDazxrAeEtCCBZCDZ3l8fBAFaSEX2DyqDAIeIP27/AIh6fCVEAU3By14ZTmk5RNocCh55G0DKH4nXyQoJuG40FJzFAtWbzQAM1P8ARRC6bc80ZbwAM5lg49VvbWcyAqNzpuQ5UqxkxjK0HI0UuMpQcFx8c0IwnbaLaK+lodPQpAIkjpTuXk+eQ39KsJSzi2mp49mwr0btH8CAQBt/jgxGXjfJ+sUeEYCAPyDlJic5IiNaVCqE0MsspJDaogxNap0li51SkKcC5ZdBcBjVUCAyWANlYl8c0+k1OJ3WqjAyyRTewV/hBwPAuJXSoROkIbUyTM31z8TUbgSC9qmbLRp8CTQmG7rBfgw+AVrDldOc3m7TpYFoCYDVq27qE0tuMQGiyJALfxF6dWYADejfuaUt6CLtZukJZdqbf8mGndkXUbH8/f/aAAwDAQACAAMAAAAQ888888888888888888888888888888888888888888888888888886z2x7yz8588888d7qfEWL+o288N9sNPNec7R988OeNMsO9ede8888888888888888888888888888888888888888888888888888888888888888888//EACcRAQACAgECBQQDAAAAAAAAAAEAESExQWFxEFGB4fAgUGCRocHR/9oACAEDAQE/EPuqA6I9UAcoEvCF3VxFwR6AeUyxJt0Hd+MX4nYm/wBIX6Z6fR8XaNd294ppxUOH83EsvEIBNZ/uJt295Vx9Zp2rrdUZ9C063FqJOSprC9brPWAlyPf+b8VFNy+uNULlzRuGUFRyDc0WpQipviOzSf75PHayHxXyoK7Vt68d9LeXxGITy8UmW4pqX7mfi7ldK3LSm4VceX/BP//EACkRAAIBAwEHAwUAAAAAAAAAAAERACExQVFhcaGx0eHwIJHBEFBggfH/2gAIAQIBAT8Q+6pXV0NkBbOId0kDSAyUprCQwwNIstXQ2gtnEMaSBpFAiAR3ejgTyMMQqJPyoWBYT4iCsMPkYQAklIAAtr8wmrsrf04RHOIoxyhk3IfPaGgAWDebJP6gOH2KYKmv7cMAOih8wBZwkANy8EoOHQqBxDsIDdT36jWW8E3PoBkCxmm2vMIFaDv1lELd/P7HSfPPiV9G6SkDfQ9ZT1uMEv26QKabX+Cf/8QAJxABAQACAgIBBAICAwAAAAAAAREAITFBUWFxECCRoYHRcPBAscH/2gAIAQEAAT8Q/wAxtqUDmTjso1mpkfnCkEY5BcaQxUfADiG6FTOtyfCL2cYMCxr6+f0TGQSU+kQVOtotFQeMMRu3B2UMW6P9PGCR7sv5KX4cCPJou0PknQKF1Rgj6j82EU8UMBWtOFwbBGOK8gyFVX+uXEk0Dv4WJ8IvZxgJJaq/qoP4mcNwZHWXdgd0OwVMQi4pN0hTV7spoTeclxYY9cGCh1UhoeL2hPSoEYwhRHhH76DJ1baJH3+6XBqFT77A4HNpRaEVzJZokpxfaHFz9lQIBOladjkGQACAln5WP18HesAiUNON64iP4AH4cch9+l4I5aLuHVxRayqln2voIh7k1zm/yP8AMGdVYw8M8A8F34ihp6fsCBujOHVxs+qcblqo81V1WExL8oQZ0XuxO44xZvBoBDZVVN6CMcC8s9We7s+3ePHMpXgXbtl3tOsoxINot8Eevv0GQO4d+Zn/AG4Z2EPx/d9daaudP3z9xmo0hQ7lVoPnOLKaavJlK9gPeAMb6INZ08f6RDZH00T8/wDSZKX7DYQeafZFnDg04BhouYQ3cm8q78U8wlYuDnZiilnfLM+PxsZMOsKlXRAnuO/obBMULL9g+NeRxB5+IlL8ND0Ptl+VE1DtVAPeBkJ0yakCoDyuPcNNSRRUKS8ZKqW6igRSsv0X5BqfcooBPWAYIlV2FspI945INHp/OXVS0E/lIGBPm2bYIeDQq7HCrxubQgfKGC1AdPRED842q5OGa3oAj63SmImGBQdbRu2PgspYAIOcbUJ8awYSo3ZgoPIVjFiTDLAiiieMcvvkgIH6d99FBATLReCqHUGZv4jwZ32ba+UN2HzqYEQAcAEn/GQREo4jEsDZspT2EXZzQvBDDEADQB19xsx3SYzttJN3FjQdZFIkYAa8uEacpua64CDAbOaafu4DGoOk8jEI9aCIOCQV6c8Zs3+bhTuCKgq7gwI3hDsbwr1xbxKuIIGueEUvkRv0u2uvoyOA1b8rBwf+5uiixK92QAjtm/polN3Fd4Q6CkWGKmEEJkLaSAbXBpLTCjDbzntTamC81cOdB5PjBDMFshYJrQCZ2YU1kRU3wCtwBFd5sQoXNew6ha3S/wCfv//Z</t>
         </is>
       </c>
     </row>

--- a/database.xlsx
+++ b/database.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,32 +508,6 @@
         <is>
           <t>Limit</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>renzo.r</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>54321</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>renzo rocha</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Full-Time</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,6 +508,36 @@
         <is>
           <t>Limit</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>renzo.r</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>54321</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>renzo rocha</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,36 +508,6 @@
         <is>
           <t>Limit</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>renzo.r</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>54321</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>renzo rocha</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Full-Time</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>175</v>
       </c>
     </row>
   </sheetData>
